--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_27_44.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_27_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2167172.968459686</v>
+        <v>2167347.826340978</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8253699.463162357</v>
+        <v>8248571.364695199</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11327186.03578608</v>
+        <v>11336604.71754492</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5049833.447741186</v>
+        <v>5049870.684558396</v>
       </c>
     </row>
     <row r="11">
@@ -8667,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>153.0459045266863</v>
+        <v>152.0931294520981</v>
       </c>
       <c r="K11" t="n">
         <v>220.0898510449805</v>
@@ -8688,7 +8688,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
-        <v>194.3056898744495</v>
+        <v>193.3529147998613</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,13 +8746,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>98.83762666666669</v>
+        <v>97.88485159207848</v>
       </c>
       <c r="K12" t="n">
         <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>117.9506061949685</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
@@ -8764,10 +8764,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>105.9744074143302</v>
+        <v>112.6695351896322</v>
       </c>
       <c r="Q12" t="n">
-        <v>139.9817740860215</v>
+        <v>111.0289990114333</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>101.0132581705354</v>
+        <v>100.0604830959472</v>
       </c>
       <c r="L13" t="n">
-        <v>106.8846762812383</v>
+        <v>105.9319012066501</v>
       </c>
       <c r="M13" t="n">
-        <v>110.9257839476051</v>
+        <v>109.9730088730168</v>
       </c>
       <c r="N13" t="n">
-        <v>99.68554446523319</v>
+        <v>98.73276939064498</v>
       </c>
       <c r="O13" t="n">
-        <v>110.4565384518428</v>
+        <v>109.5037633772546</v>
       </c>
       <c r="P13" t="n">
-        <v>109.7280040491476</v>
+        <v>108.7752289745594</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,7 +8904,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>87.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K14" t="n">
         <v>220.0898510449805</v>
@@ -8925,7 +8925,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
-        <v>128.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8980,16 +8980,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5.522379999999998</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J15" t="n">
-        <v>32.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>69.14317436020005</v>
       </c>
       <c r="L15" t="n">
-        <v>69.02184022327387</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
         <v>142.1340339220183</v>
@@ -8998,13 +8998,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>142.5962444444444</v>
+        <v>49.23706432777166</v>
       </c>
       <c r="P15" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>45.98177408602152</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,25 +9065,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>35.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L16" t="n">
-        <v>40.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M16" t="n">
-        <v>44.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N16" t="n">
-        <v>33.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O16" t="n">
-        <v>44.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P16" t="n">
-        <v>43.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q16" t="n">
-        <v>57.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9141,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>87.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K17" t="n">
         <v>220.0898510449805</v>
@@ -9162,7 +9162,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
-        <v>128.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9217,10 +9217,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5.522379999999998</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J18" t="n">
-        <v>32.83762666666669</v>
+        <v>58.1393620525083</v>
       </c>
       <c r="K18" t="n">
         <v>137.841438974359</v>
@@ -9235,10 +9235,10 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>48.59624444444444</v>
+        <v>49.23706432777166</v>
       </c>
       <c r="P18" t="n">
-        <v>64.44186785772997</v>
+        <v>40.61522729765747</v>
       </c>
       <c r="Q18" t="n">
         <v>139.9817740860215</v>
@@ -9302,25 +9302,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>35.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L19" t="n">
-        <v>40.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M19" t="n">
-        <v>44.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N19" t="n">
-        <v>33.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O19" t="n">
-        <v>44.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P19" t="n">
-        <v>43.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q19" t="n">
-        <v>57.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>87.04590452668629</v>
+        <v>87.68672441001351</v>
       </c>
       <c r="K20" t="n">
         <v>220.0898510449805</v>
@@ -9399,7 +9399,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q20" t="n">
-        <v>128.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9454,19 +9454,19 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>5.522379999999998</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J21" t="n">
-        <v>32.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K21" t="n">
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>44.55437977987418</v>
+        <v>69.85611516571524</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>48.77485380534554</v>
       </c>
       <c r="N21" t="n">
         <v>131.3417120833333</v>
@@ -9478,7 +9478,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.44923452942125</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,25 +9539,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>35.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L22" t="n">
-        <v>40.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M22" t="n">
-        <v>44.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N22" t="n">
-        <v>33.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O22" t="n">
-        <v>44.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P22" t="n">
-        <v>43.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q22" t="n">
-        <v>57.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -9615,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>87.04590452668629</v>
+        <v>100.8226894515544</v>
       </c>
       <c r="K23" t="n">
         <v>220.0898510449805</v>
@@ -9636,7 +9636,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q23" t="n">
-        <v>128.3056898744495</v>
+        <v>128.9465097577767</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9691,16 +9691,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>5.522379999999998</v>
+        <v>6.163199883327223</v>
       </c>
       <c r="J24" t="n">
-        <v>32.83762666666669</v>
+        <v>33.47844654999392</v>
       </c>
       <c r="K24" t="n">
         <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>69.02184022327391</v>
+        <v>45.19519966320141</v>
       </c>
       <c r="M24" t="n">
         <v>142.1340339220183</v>
@@ -9709,10 +9709,10 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>142.5962444444444</v>
+        <v>49.23706432777166</v>
       </c>
       <c r="P24" t="n">
-        <v>39.97440741433024</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
         <v>139.9817740860215</v>
@@ -9776,25 +9776,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>35.01325817053538</v>
+        <v>35.65407805386261</v>
       </c>
       <c r="L25" t="n">
-        <v>40.88467628123828</v>
+        <v>41.52549616456551</v>
       </c>
       <c r="M25" t="n">
-        <v>44.92578394760505</v>
+        <v>45.56660383093228</v>
       </c>
       <c r="N25" t="n">
-        <v>33.68554446523319</v>
+        <v>34.32636434856042</v>
       </c>
       <c r="O25" t="n">
-        <v>44.45653845184279</v>
+        <v>45.09735833517001</v>
       </c>
       <c r="P25" t="n">
-        <v>43.72800404914761</v>
+        <v>44.36882393247484</v>
       </c>
       <c r="Q25" t="n">
-        <v>57.50500162944584</v>
+        <v>58.14582151277307</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>97.04590452668629</v>
+        <v>91.64927167527121</v>
       </c>
       <c r="K26" t="n">
         <v>220.0898510449805</v>
@@ -9873,7 +9873,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q26" t="n">
-        <v>138.3056898744495</v>
+        <v>132.9090570230344</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,13 +9931,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>65.02630591194972</v>
+        <v>37.44099381525162</v>
       </c>
       <c r="K27" t="n">
-        <v>53.84143897435899</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>54.55437977987418</v>
+        <v>49.1577469284591</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -9952,7 +9952,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>74.19934613875235</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,25 +10013,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>45.01325817053538</v>
+        <v>39.6166253191203</v>
       </c>
       <c r="L28" t="n">
-        <v>50.88467628123828</v>
+        <v>45.48804342982321</v>
       </c>
       <c r="M28" t="n">
-        <v>54.92578394760505</v>
+        <v>49.52915109618998</v>
       </c>
       <c r="N28" t="n">
-        <v>43.68554446523319</v>
+        <v>38.28891161381812</v>
       </c>
       <c r="O28" t="n">
-        <v>54.45653845184279</v>
+        <v>49.05990560042771</v>
       </c>
       <c r="P28" t="n">
-        <v>53.72800404914761</v>
+        <v>48.33137119773254</v>
       </c>
       <c r="Q28" t="n">
-        <v>65.34295837775146</v>
+        <v>62.10836877803077</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>44.04590452668629</v>
+        <v>43.82023248085932</v>
       </c>
       <c r="K29" t="n">
         <v>220.0898510449805</v>
@@ -10110,7 +10110,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
-        <v>85.30568987444948</v>
+        <v>85.08001782862252</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,31 +10168,31 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>118.0026406320524</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>0.6157669285320253</v>
       </c>
       <c r="L30" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>5.134033922018318</v>
+        <v>127.1529087526293</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>5.596244444444437</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.981774086021517</v>
+        <v>2.756102040194548</v>
       </c>
       <c r="R30" t="n">
-        <v>8.679503963963953</v>
+        <v>8.453831918136984</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -10259,16 +10259,16 @@
         <v>138.9257839476051</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O31" t="n">
-        <v>138.4565384518428</v>
+        <v>1.230866406015821</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7280040491476143</v>
+        <v>0.502332003320646</v>
       </c>
       <c r="Q31" t="n">
-        <v>14.50500162944584</v>
+        <v>14.27932958361887</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -10326,7 +10326,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>44.04590452668629</v>
+        <v>43.82023248085932</v>
       </c>
       <c r="K32" t="n">
         <v>220.0898510449805</v>
@@ -10347,7 +10347,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q32" t="n">
-        <v>85.30568987444948</v>
+        <v>85.08001782862252</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,31 +10405,31 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>51.38609205896422</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8414389743589936</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>1.328707734047214</v>
       </c>
       <c r="M33" t="n">
-        <v>5.134033922018318</v>
+        <v>12.4101621542614</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>5.596244444444437</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.981774086021517</v>
+        <v>2.756102040194548</v>
       </c>
       <c r="R33" t="n">
-        <v>8.679503963963953</v>
+        <v>45.52166981132082</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -10502,10 +10502,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P34" t="n">
-        <v>0.7280040491476143</v>
+        <v>0.502332003320646</v>
       </c>
       <c r="Q34" t="n">
-        <v>14.50500162944584</v>
+        <v>14.27932958361887</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>44.04590452668629</v>
+        <v>43.82023248085932</v>
       </c>
       <c r="K35" t="n">
         <v>220.0898510449805</v>
@@ -10584,7 +10584,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
-        <v>85.30568987444948</v>
+        <v>85.08001782862252</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,22 +10642,22 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>50.45359813374644</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8414389743589936</v>
+        <v>0.6157669285320253</v>
       </c>
       <c r="L36" t="n">
-        <v>47.28218392217174</v>
+        <v>1.328707734047214</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>4.90836187619135</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>5.596244444444437</v>
+        <v>5.370572398617469</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -10666,7 +10666,7 @@
         <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
-        <v>8.679503963963953</v>
+        <v>8.453831918136984</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -10739,10 +10739,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P37" t="n">
-        <v>0.7280040491476143</v>
+        <v>0.502332003320646</v>
       </c>
       <c r="Q37" t="n">
-        <v>14.50500162944584</v>
+        <v>14.27932958361887</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>44.04590452668629</v>
+        <v>43.82023248085932</v>
       </c>
       <c r="K38" t="n">
         <v>220.0898510449805</v>
@@ -10821,7 +10821,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q38" t="n">
-        <v>85.30568987444948</v>
+        <v>85.08001782862252</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10882,25 +10882,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8414389743589936</v>
+        <v>0.6157669285320253</v>
       </c>
       <c r="L39" t="n">
-        <v>1.554379779874182</v>
+        <v>1.328707734047214</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>4.90836187619135</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>5.596244444444437</v>
+        <v>5.370572398617469</v>
       </c>
       <c r="P39" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.981774086021517</v>
+        <v>2.756102040194548</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10958,7 +10958,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>29.39207727397414</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -10976,10 +10976,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P40" t="n">
-        <v>21.77117860489204</v>
+        <v>0.502332003320646</v>
       </c>
       <c r="Q40" t="n">
-        <v>14.50500162944584</v>
+        <v>14.27932958361887</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -11037,7 +11037,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>62.04590452668629</v>
+        <v>68.81046029018982</v>
       </c>
       <c r="K41" t="n">
         <v>220.0898510449805</v>
@@ -11058,7 +11058,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
-        <v>142.6778496194181</v>
+        <v>110.070245637953</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>7.837626666666694</v>
+        <v>14.60218243017023</v>
       </c>
       <c r="K42" t="n">
-        <v>18.84143897435899</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>26.31893554337772</v>
       </c>
       <c r="M42" t="n">
-        <v>23.13403392201832</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>12.34171208333331</v>
+        <v>106.5510377629822</v>
       </c>
       <c r="O42" t="n">
-        <v>23.59624444444444</v>
+        <v>30.36080020794797</v>
       </c>
       <c r="P42" t="n">
-        <v>14.97440741433024</v>
+        <v>21.73896317783378</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>27.74632984952505</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11195,10 +11195,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>7.995421439396111</v>
+        <v>14.75997720289965</v>
       </c>
       <c r="K43" t="n">
-        <v>10.01325817053538</v>
+        <v>16.77781393403892</v>
       </c>
       <c r="L43" t="n">
         <v>134.8846762812383</v>
@@ -11213,10 +11213,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P43" t="n">
-        <v>18.72800404914761</v>
+        <v>25.49255981265115</v>
       </c>
       <c r="Q43" t="n">
-        <v>32.50500162944584</v>
+        <v>39.26955739294938</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>354.7338416634806</v>
+        <v>353.7810665888924</v>
       </c>
       <c r="C11" t="n">
-        <v>337.2728917710076</v>
+        <v>336.3201166964193</v>
       </c>
       <c r="D11" t="n">
-        <v>326.683041620683</v>
+        <v>325.7302665460948</v>
       </c>
       <c r="E11" t="n">
-        <v>353.9303700722618</v>
+        <v>352.9775949976736</v>
       </c>
       <c r="F11" t="n">
-        <v>378.8760457417114</v>
+        <v>377.9232706671232</v>
       </c>
       <c r="G11" t="n">
-        <v>387.302737515135</v>
+        <v>386.3499624405468</v>
       </c>
       <c r="H11" t="n">
-        <v>311.4748021157671</v>
+        <v>310.5220270411789</v>
       </c>
       <c r="I11" t="n">
-        <v>182.4758895704059</v>
+        <v>181.5231144958177</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>121.8691179411497</v>
+        <v>120.9163428665615</v>
       </c>
       <c r="S11" t="n">
-        <v>181.0200695862453</v>
+        <v>180.0672945116571</v>
       </c>
       <c r="T11" t="n">
-        <v>195.0958495641314</v>
+        <v>194.1430744895432</v>
       </c>
       <c r="U11" t="n">
-        <v>223.3456529078365</v>
+        <v>222.3928778332483</v>
       </c>
       <c r="V11" t="n">
-        <v>299.7522584701349</v>
+        <v>298.7994833955467</v>
       </c>
       <c r="W11" t="n">
-        <v>321.240968717413</v>
+        <v>320.2881936428248</v>
       </c>
       <c r="X11" t="n">
-        <v>341.731100678469</v>
+        <v>340.7783256038808</v>
       </c>
       <c r="Y11" t="n">
-        <v>358.2379386560536</v>
+        <v>357.2851635814654</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>138.5331836498673</v>
+        <v>137.5804085752791</v>
       </c>
       <c r="C12" t="n">
-        <v>144.7084989883157</v>
+        <v>143.7557239137275</v>
       </c>
       <c r="D12" t="n">
-        <v>119.4450655646388</v>
+        <v>118.4922904900505</v>
       </c>
       <c r="E12" t="n">
-        <v>129.6450804554009</v>
+        <v>128.6923053808127</v>
       </c>
       <c r="F12" t="n">
-        <v>117.0692123933839</v>
+        <v>116.1164373187957</v>
       </c>
       <c r="G12" t="n">
-        <v>109.3435171632106</v>
+        <v>108.3907420886224</v>
       </c>
       <c r="H12" t="n">
-        <v>84.23544423649646</v>
+        <v>83.28266916190825</v>
       </c>
       <c r="I12" t="n">
-        <v>61.39663285141508</v>
+        <v>60.44385777682686</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>72.15783415264313</v>
+        <v>71.20505907805492</v>
       </c>
       <c r="S12" t="n">
-        <v>143.6831711038378</v>
+        <v>142.7303960292496</v>
       </c>
       <c r="T12" t="n">
-        <v>172.1647286948216</v>
+        <v>171.2119536202334</v>
       </c>
       <c r="U12" t="n">
-        <v>197.9413820809748</v>
+        <v>196.9886070063866</v>
       </c>
       <c r="V12" t="n">
-        <v>204.8005871494253</v>
+        <v>203.8478120748371</v>
       </c>
       <c r="W12" t="n">
-        <v>223.6949831609196</v>
+        <v>222.7422080863314</v>
       </c>
       <c r="X12" t="n">
-        <v>177.7729852034775</v>
+        <v>176.8202101288892</v>
       </c>
       <c r="Y12" t="n">
-        <v>177.6826957773044</v>
+        <v>176.7299207027161</v>
       </c>
     </row>
     <row r="13">
@@ -23373,31 +23373,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>151.8319801819373</v>
+        <v>150.8792051073491</v>
       </c>
       <c r="C13" t="n">
-        <v>139.2468210986278</v>
+        <v>138.2940460240396</v>
       </c>
       <c r="D13" t="n">
-        <v>120.6154730182124</v>
+        <v>119.6626979436241</v>
       </c>
       <c r="E13" t="n">
-        <v>118.4339626465692</v>
+        <v>117.481187571981</v>
       </c>
       <c r="F13" t="n">
-        <v>117.4210480229312</v>
+        <v>116.468272948343</v>
       </c>
       <c r="G13" t="n">
-        <v>139.9909793584588</v>
+        <v>139.0382042838705</v>
       </c>
       <c r="H13" t="n">
-        <v>134.2271725074396</v>
+        <v>133.2743974328513</v>
       </c>
       <c r="I13" t="n">
-        <v>127.4504749272583</v>
+        <v>126.4976998526701</v>
       </c>
       <c r="J13" t="n">
-        <v>65.35918011667277</v>
+        <v>64.40640504208456</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>58.16204325169439</v>
+        <v>57.20926817710617</v>
       </c>
       <c r="R13" t="n">
-        <v>149.2933913771695</v>
+        <v>148.3406163025813</v>
       </c>
       <c r="S13" t="n">
-        <v>196.0165980369723</v>
+        <v>195.0638229623841</v>
       </c>
       <c r="T13" t="n">
-        <v>199.9455894282815</v>
+        <v>198.9928143536933</v>
       </c>
       <c r="U13" t="n">
-        <v>258.3190293564909</v>
+        <v>257.3662542819027</v>
       </c>
       <c r="V13" t="n">
-        <v>224.137643323828</v>
+        <v>223.1848682492398</v>
       </c>
       <c r="W13" t="n">
-        <v>258.522998336591</v>
+        <v>257.5702232620028</v>
       </c>
       <c r="X13" t="n">
-        <v>197.7096553890372</v>
+        <v>196.7568803144489</v>
       </c>
       <c r="Y13" t="n">
-        <v>190.5846533520948</v>
+        <v>189.6318782775066</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C14" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D14" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E14" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F14" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G14" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H14" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I14" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S14" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T14" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U14" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V14" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W14" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X14" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y14" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C15" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D15" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E15" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F15" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G15" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H15" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S15" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T15" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U15" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V15" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W15" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X15" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y15" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="16">
@@ -23610,28 +23610,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C16" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D16" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E16" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F16" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G16" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H16" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I16" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S16" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T16" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U16" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V16" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W16" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X16" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y16" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C17" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D17" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E17" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F17" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G17" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H17" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I17" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S17" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T17" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U17" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V17" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W17" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X17" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y17" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C18" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D18" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E18" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F18" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G18" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H18" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S18" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T18" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U18" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V18" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W18" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X18" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y18" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="19">
@@ -23847,28 +23847,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C19" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D19" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E19" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F19" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G19" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H19" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I19" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S19" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T19" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U19" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V19" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W19" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X19" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y19" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C20" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D20" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E20" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F20" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G20" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H20" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I20" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S20" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T20" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U20" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V20" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W20" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X20" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y20" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C21" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D21" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E21" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F21" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G21" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H21" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S21" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T21" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U21" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V21" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W21" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X21" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y21" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="22">
@@ -24084,28 +24084,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C22" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D22" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E22" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F22" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G22" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H22" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I22" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S22" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T22" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U22" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V22" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W22" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X22" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y22" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C23" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D23" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E23" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F23" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G23" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H23" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I23" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S23" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T23" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U23" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V23" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W23" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X23" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y23" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C24" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D24" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E24" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F24" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G24" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H24" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S24" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T24" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U24" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V24" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W24" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X24" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y24" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="25">
@@ -24321,28 +24321,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C25" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D25" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E25" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F25" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G25" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H25" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I25" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S25" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T25" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U25" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V25" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W25" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X25" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y25" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>298.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C26" t="n">
-        <v>281.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D26" t="n">
-        <v>270.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E26" t="n">
-        <v>297.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F26" t="n">
-        <v>322.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G26" t="n">
-        <v>331.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H26" t="n">
-        <v>255.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I26" t="n">
-        <v>126.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>65.86911794114968</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S26" t="n">
-        <v>125.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T26" t="n">
-        <v>139.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U26" t="n">
-        <v>167.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V26" t="n">
-        <v>243.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W26" t="n">
-        <v>265.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X26" t="n">
-        <v>285.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y26" t="n">
-        <v>302.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="27">
@@ -24479,28 +24479,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>82.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C27" t="n">
-        <v>88.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D27" t="n">
-        <v>63.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E27" t="n">
-        <v>73.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F27" t="n">
-        <v>61.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G27" t="n">
-        <v>53.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H27" t="n">
-        <v>28.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I27" t="n">
-        <v>5.396632851415077</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>16.15783415264313</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S27" t="n">
-        <v>87.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T27" t="n">
-        <v>116.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U27" t="n">
-        <v>141.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V27" t="n">
-        <v>148.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W27" t="n">
-        <v>167.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X27" t="n">
-        <v>121.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y27" t="n">
-        <v>121.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>95.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C28" t="n">
-        <v>83.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D28" t="n">
-        <v>64.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E28" t="n">
-        <v>62.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F28" t="n">
-        <v>61.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G28" t="n">
-        <v>83.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H28" t="n">
-        <v>78.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I28" t="n">
-        <v>71.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J28" t="n">
-        <v>9.359180116672775</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,31 +24603,31 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.162043251694385</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>93.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S28" t="n">
-        <v>140.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T28" t="n">
-        <v>143.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U28" t="n">
-        <v>202.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V28" t="n">
-        <v>168.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W28" t="n">
-        <v>202.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X28" t="n">
-        <v>141.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y28" t="n">
-        <v>134.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>245.7338416634806</v>
+        <v>245.5081696176536</v>
       </c>
       <c r="C29" t="n">
-        <v>228.2728917710076</v>
+        <v>228.0472197251806</v>
       </c>
       <c r="D29" t="n">
-        <v>217.683041620683</v>
+        <v>217.457369574856</v>
       </c>
       <c r="E29" t="n">
-        <v>244.9303700722618</v>
+        <v>244.7046980264348</v>
       </c>
       <c r="F29" t="n">
-        <v>269.8760457417114</v>
+        <v>269.6503736958845</v>
       </c>
       <c r="G29" t="n">
-        <v>278.302737515135</v>
+        <v>278.0770654693081</v>
       </c>
       <c r="H29" t="n">
-        <v>202.4748021157671</v>
+        <v>202.2491300699402</v>
       </c>
       <c r="I29" t="n">
-        <v>73.47588957040591</v>
+        <v>73.25021752457894</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>12.86911794114968</v>
+        <v>12.64344589532271</v>
       </c>
       <c r="S29" t="n">
-        <v>72.02006958624534</v>
+        <v>71.79439754041837</v>
       </c>
       <c r="T29" t="n">
-        <v>86.09584956413136</v>
+        <v>85.87017751830439</v>
       </c>
       <c r="U29" t="n">
-        <v>114.3456529078365</v>
+        <v>114.1199808620095</v>
       </c>
       <c r="V29" t="n">
-        <v>190.7522584701349</v>
+        <v>190.5265864243079</v>
       </c>
       <c r="W29" t="n">
-        <v>212.240968717413</v>
+        <v>212.015296671586</v>
       </c>
       <c r="X29" t="n">
-        <v>232.731100678469</v>
+        <v>232.5054286326421</v>
       </c>
       <c r="Y29" t="n">
-        <v>249.2379386560536</v>
+        <v>249.0122666102266</v>
       </c>
     </row>
     <row r="30">
@@ -24716,22 +24716,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29.53318364986734</v>
+        <v>29.30751160404037</v>
       </c>
       <c r="C30" t="n">
-        <v>35.70849898831574</v>
+        <v>35.48282694248877</v>
       </c>
       <c r="D30" t="n">
-        <v>10.44506556463875</v>
+        <v>10.21939351881178</v>
       </c>
       <c r="E30" t="n">
-        <v>20.64508045540094</v>
+        <v>20.41940840957398</v>
       </c>
       <c r="F30" t="n">
-        <v>8.069212393383879</v>
+        <v>7.84354034755691</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3435171632106346</v>
+        <v>0.1178451173836663</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>34.68317110383782</v>
+        <v>34.45749905801085</v>
       </c>
       <c r="T30" t="n">
-        <v>63.1647286948216</v>
+        <v>62.93905664899464</v>
       </c>
       <c r="U30" t="n">
-        <v>88.94138208097482</v>
+        <v>88.71571003514785</v>
       </c>
       <c r="V30" t="n">
-        <v>95.80058714942527</v>
+        <v>95.5749151035983</v>
       </c>
       <c r="W30" t="n">
-        <v>114.6949831609196</v>
+        <v>114.4693111150926</v>
       </c>
       <c r="X30" t="n">
-        <v>68.77298520347748</v>
+        <v>68.54731315765051</v>
       </c>
       <c r="Y30" t="n">
-        <v>68.68269577730436</v>
+        <v>68.45702373147739</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>42.8319801819373</v>
+        <v>42.60630813611033</v>
       </c>
       <c r="C31" t="n">
-        <v>30.24682109862783</v>
+        <v>30.02114905280087</v>
       </c>
       <c r="D31" t="n">
-        <v>11.61547301821236</v>
+        <v>11.38980097238539</v>
       </c>
       <c r="E31" t="n">
-        <v>9.433962646569171</v>
+        <v>9.208290600742203</v>
       </c>
       <c r="F31" t="n">
-        <v>8.421048022931245</v>
+        <v>8.195375977104277</v>
       </c>
       <c r="G31" t="n">
-        <v>30.99097935845876</v>
+        <v>30.76530731263179</v>
       </c>
       <c r="H31" t="n">
-        <v>25.22717250743958</v>
+        <v>25.00150046161261</v>
       </c>
       <c r="I31" t="n">
-        <v>18.45047492725828</v>
+        <v>18.22480288143132</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>40.29339137716948</v>
+        <v>40.06771933134252</v>
       </c>
       <c r="S31" t="n">
-        <v>87.01659803697225</v>
+        <v>86.79092599114529</v>
       </c>
       <c r="T31" t="n">
-        <v>90.94558942828149</v>
+        <v>90.71991738245453</v>
       </c>
       <c r="U31" t="n">
-        <v>149.3190293564909</v>
+        <v>149.0933573106639</v>
       </c>
       <c r="V31" t="n">
-        <v>115.137643323828</v>
+        <v>114.911971278001</v>
       </c>
       <c r="W31" t="n">
-        <v>149.522998336591</v>
+        <v>149.297326290764</v>
       </c>
       <c r="X31" t="n">
-        <v>88.70965538903715</v>
+        <v>88.48398334321018</v>
       </c>
       <c r="Y31" t="n">
-        <v>81.58465335209479</v>
+        <v>81.35898130626782</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>245.7338416634806</v>
+        <v>245.5081696176536</v>
       </c>
       <c r="C32" t="n">
-        <v>228.2728917710076</v>
+        <v>228.0472197251806</v>
       </c>
       <c r="D32" t="n">
-        <v>217.683041620683</v>
+        <v>217.457369574856</v>
       </c>
       <c r="E32" t="n">
-        <v>244.9303700722618</v>
+        <v>244.7046980264348</v>
       </c>
       <c r="F32" t="n">
-        <v>269.8760457417114</v>
+        <v>269.6503736958845</v>
       </c>
       <c r="G32" t="n">
-        <v>278.302737515135</v>
+        <v>278.0770654693081</v>
       </c>
       <c r="H32" t="n">
-        <v>202.4748021157671</v>
+        <v>202.2491300699402</v>
       </c>
       <c r="I32" t="n">
-        <v>73.47588957040591</v>
+        <v>73.25021752457894</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>12.86911794114968</v>
+        <v>12.64344589532271</v>
       </c>
       <c r="S32" t="n">
-        <v>72.02006958624534</v>
+        <v>71.79439754041837</v>
       </c>
       <c r="T32" t="n">
-        <v>86.09584956413136</v>
+        <v>85.87017751830439</v>
       </c>
       <c r="U32" t="n">
-        <v>114.3456529078365</v>
+        <v>114.1199808620095</v>
       </c>
       <c r="V32" t="n">
-        <v>190.7522584701349</v>
+        <v>190.5265864243079</v>
       </c>
       <c r="W32" t="n">
-        <v>212.240968717413</v>
+        <v>212.015296671586</v>
       </c>
       <c r="X32" t="n">
-        <v>232.731100678469</v>
+        <v>232.5054286326421</v>
       </c>
       <c r="Y32" t="n">
-        <v>249.2379386560536</v>
+        <v>249.0122666102266</v>
       </c>
     </row>
     <row r="33">
@@ -24953,22 +24953,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.53318364986734</v>
+        <v>29.30751160404037</v>
       </c>
       <c r="C33" t="n">
-        <v>35.70849898831574</v>
+        <v>35.48282694248877</v>
       </c>
       <c r="D33" t="n">
-        <v>10.44506556463875</v>
+        <v>10.21939351881178</v>
       </c>
       <c r="E33" t="n">
-        <v>20.64508045540094</v>
+        <v>20.41940840957398</v>
       </c>
       <c r="F33" t="n">
-        <v>8.069212393383879</v>
+        <v>7.84354034755691</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3435171632106346</v>
+        <v>0.1178451173836663</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>34.68317110383782</v>
+        <v>34.45749905801085</v>
       </c>
       <c r="T33" t="n">
-        <v>63.1647286948216</v>
+        <v>62.93905664899464</v>
       </c>
       <c r="U33" t="n">
-        <v>88.94138208097482</v>
+        <v>88.71571003514785</v>
       </c>
       <c r="V33" t="n">
-        <v>95.80058714942527</v>
+        <v>95.5749151035983</v>
       </c>
       <c r="W33" t="n">
-        <v>114.6949831609196</v>
+        <v>114.4693111150926</v>
       </c>
       <c r="X33" t="n">
-        <v>68.77298520347748</v>
+        <v>68.54731315765051</v>
       </c>
       <c r="Y33" t="n">
-        <v>68.68269577730436</v>
+        <v>68.45702373147739</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>42.8319801819373</v>
+        <v>42.60630813611033</v>
       </c>
       <c r="C34" t="n">
-        <v>30.24682109862783</v>
+        <v>30.02114905280087</v>
       </c>
       <c r="D34" t="n">
-        <v>11.61547301821236</v>
+        <v>11.38980097238539</v>
       </c>
       <c r="E34" t="n">
-        <v>9.433962646569171</v>
+        <v>9.208290600742203</v>
       </c>
       <c r="F34" t="n">
-        <v>8.421048022931245</v>
+        <v>8.195375977104277</v>
       </c>
       <c r="G34" t="n">
-        <v>30.99097935845876</v>
+        <v>30.76530731263179</v>
       </c>
       <c r="H34" t="n">
-        <v>25.22717250743958</v>
+        <v>25.00150046161261</v>
       </c>
       <c r="I34" t="n">
-        <v>18.45047492725828</v>
+        <v>18.22480288143132</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>40.29339137716948</v>
+        <v>40.06771933134252</v>
       </c>
       <c r="S34" t="n">
-        <v>87.01659803697225</v>
+        <v>86.79092599114529</v>
       </c>
       <c r="T34" t="n">
-        <v>90.94558942828149</v>
+        <v>90.71991738245453</v>
       </c>
       <c r="U34" t="n">
-        <v>149.3190293564909</v>
+        <v>149.0933573106639</v>
       </c>
       <c r="V34" t="n">
-        <v>115.137643323828</v>
+        <v>114.911971278001</v>
       </c>
       <c r="W34" t="n">
-        <v>149.522998336591</v>
+        <v>149.297326290764</v>
       </c>
       <c r="X34" t="n">
-        <v>88.70965538903715</v>
+        <v>88.48398334321018</v>
       </c>
       <c r="Y34" t="n">
-        <v>81.58465335209479</v>
+        <v>81.35898130626782</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>245.7338416634806</v>
+        <v>245.5081696176536</v>
       </c>
       <c r="C35" t="n">
-        <v>228.2728917710076</v>
+        <v>228.0472197251806</v>
       </c>
       <c r="D35" t="n">
-        <v>217.683041620683</v>
+        <v>217.457369574856</v>
       </c>
       <c r="E35" t="n">
-        <v>244.9303700722618</v>
+        <v>244.7046980264348</v>
       </c>
       <c r="F35" t="n">
-        <v>269.8760457417114</v>
+        <v>269.6503736958845</v>
       </c>
       <c r="G35" t="n">
-        <v>278.302737515135</v>
+        <v>278.0770654693081</v>
       </c>
       <c r="H35" t="n">
-        <v>202.4748021157671</v>
+        <v>202.2491300699402</v>
       </c>
       <c r="I35" t="n">
-        <v>73.47588957040591</v>
+        <v>73.25021752457894</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>12.86911794114968</v>
+        <v>12.64344589532271</v>
       </c>
       <c r="S35" t="n">
-        <v>72.02006958624534</v>
+        <v>71.79439754041837</v>
       </c>
       <c r="T35" t="n">
-        <v>86.09584956413136</v>
+        <v>85.87017751830439</v>
       </c>
       <c r="U35" t="n">
-        <v>114.3456529078365</v>
+        <v>114.1199808620095</v>
       </c>
       <c r="V35" t="n">
-        <v>190.7522584701349</v>
+        <v>190.5265864243079</v>
       </c>
       <c r="W35" t="n">
-        <v>212.240968717413</v>
+        <v>212.015296671586</v>
       </c>
       <c r="X35" t="n">
-        <v>232.731100678469</v>
+        <v>232.5054286326421</v>
       </c>
       <c r="Y35" t="n">
-        <v>249.2379386560536</v>
+        <v>249.0122666102266</v>
       </c>
     </row>
     <row r="36">
@@ -25190,22 +25190,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.53318364986734</v>
+        <v>29.30751160404037</v>
       </c>
       <c r="C36" t="n">
-        <v>35.70849898831574</v>
+        <v>35.48282694248877</v>
       </c>
       <c r="D36" t="n">
-        <v>10.44506556463875</v>
+        <v>10.21939351881178</v>
       </c>
       <c r="E36" t="n">
-        <v>20.64508045540094</v>
+        <v>20.41940840957398</v>
       </c>
       <c r="F36" t="n">
-        <v>8.069212393383879</v>
+        <v>7.84354034755691</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3435171632106346</v>
+        <v>0.1178451173836663</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>34.68317110383782</v>
+        <v>34.45749905801085</v>
       </c>
       <c r="T36" t="n">
-        <v>63.1647286948216</v>
+        <v>62.93905664899464</v>
       </c>
       <c r="U36" t="n">
-        <v>88.94138208097482</v>
+        <v>88.71571003514785</v>
       </c>
       <c r="V36" t="n">
-        <v>95.80058714942527</v>
+        <v>95.5749151035983</v>
       </c>
       <c r="W36" t="n">
-        <v>114.6949831609196</v>
+        <v>114.4693111150926</v>
       </c>
       <c r="X36" t="n">
-        <v>68.77298520347748</v>
+        <v>68.54731315765051</v>
       </c>
       <c r="Y36" t="n">
-        <v>68.68269577730436</v>
+        <v>68.45702373147739</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>42.8319801819373</v>
+        <v>42.60630813611033</v>
       </c>
       <c r="C37" t="n">
-        <v>30.24682109862783</v>
+        <v>30.02114905280087</v>
       </c>
       <c r="D37" t="n">
-        <v>11.61547301821236</v>
+        <v>11.38980097238539</v>
       </c>
       <c r="E37" t="n">
-        <v>9.433962646569171</v>
+        <v>9.208290600742203</v>
       </c>
       <c r="F37" t="n">
-        <v>8.421048022931245</v>
+        <v>8.195375977104277</v>
       </c>
       <c r="G37" t="n">
-        <v>30.99097935845876</v>
+        <v>30.76530731263179</v>
       </c>
       <c r="H37" t="n">
-        <v>25.22717250743958</v>
+        <v>25.00150046161261</v>
       </c>
       <c r="I37" t="n">
-        <v>18.45047492725828</v>
+        <v>18.22480288143132</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>40.29339137716948</v>
+        <v>40.06771933134252</v>
       </c>
       <c r="S37" t="n">
-        <v>87.01659803697225</v>
+        <v>86.79092599114529</v>
       </c>
       <c r="T37" t="n">
-        <v>90.94558942828149</v>
+        <v>90.71991738245453</v>
       </c>
       <c r="U37" t="n">
-        <v>149.3190293564909</v>
+        <v>149.0933573106639</v>
       </c>
       <c r="V37" t="n">
-        <v>115.137643323828</v>
+        <v>114.911971278001</v>
       </c>
       <c r="W37" t="n">
-        <v>149.522998336591</v>
+        <v>149.297326290764</v>
       </c>
       <c r="X37" t="n">
-        <v>88.70965538903715</v>
+        <v>88.48398334321018</v>
       </c>
       <c r="Y37" t="n">
-        <v>81.58465335209479</v>
+        <v>81.35898130626782</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>245.7338416634806</v>
+        <v>245.5081696176536</v>
       </c>
       <c r="C38" t="n">
-        <v>228.2728917710076</v>
+        <v>228.0472197251806</v>
       </c>
       <c r="D38" t="n">
-        <v>217.683041620683</v>
+        <v>217.457369574856</v>
       </c>
       <c r="E38" t="n">
-        <v>244.9303700722618</v>
+        <v>244.7046980264348</v>
       </c>
       <c r="F38" t="n">
-        <v>269.8760457417114</v>
+        <v>269.6503736958845</v>
       </c>
       <c r="G38" t="n">
-        <v>278.302737515135</v>
+        <v>278.0770654693081</v>
       </c>
       <c r="H38" t="n">
-        <v>202.4748021157671</v>
+        <v>202.2491300699402</v>
       </c>
       <c r="I38" t="n">
-        <v>73.47588957040591</v>
+        <v>73.25021752457894</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>12.86911794114968</v>
+        <v>12.64344589532271</v>
       </c>
       <c r="S38" t="n">
-        <v>72.02006958624534</v>
+        <v>71.79439754041837</v>
       </c>
       <c r="T38" t="n">
-        <v>86.09584956413136</v>
+        <v>85.87017751830439</v>
       </c>
       <c r="U38" t="n">
-        <v>114.3456529078365</v>
+        <v>114.1199808620095</v>
       </c>
       <c r="V38" t="n">
-        <v>190.7522584701349</v>
+        <v>190.5265864243079</v>
       </c>
       <c r="W38" t="n">
-        <v>212.240968717413</v>
+        <v>212.015296671586</v>
       </c>
       <c r="X38" t="n">
-        <v>232.731100678469</v>
+        <v>232.5054286326421</v>
       </c>
       <c r="Y38" t="n">
-        <v>249.2379386560536</v>
+        <v>249.0122666102266</v>
       </c>
     </row>
     <row r="39">
@@ -25427,22 +25427,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29.53318364986734</v>
+        <v>29.30751160404037</v>
       </c>
       <c r="C39" t="n">
-        <v>35.70849898831574</v>
+        <v>35.48282694248877</v>
       </c>
       <c r="D39" t="n">
-        <v>10.44506556463875</v>
+        <v>10.21939351881178</v>
       </c>
       <c r="E39" t="n">
-        <v>20.64508045540094</v>
+        <v>20.41940840957398</v>
       </c>
       <c r="F39" t="n">
-        <v>8.069212393383879</v>
+        <v>7.84354034755691</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3435171632106346</v>
+        <v>0.1178451173836663</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>34.68317110383782</v>
+        <v>34.45749905801085</v>
       </c>
       <c r="T39" t="n">
-        <v>63.1647286948216</v>
+        <v>62.93905664899464</v>
       </c>
       <c r="U39" t="n">
-        <v>88.94138208097482</v>
+        <v>88.71571003514785</v>
       </c>
       <c r="V39" t="n">
-        <v>95.80058714942527</v>
+        <v>95.5749151035983</v>
       </c>
       <c r="W39" t="n">
-        <v>114.6949831609196</v>
+        <v>114.4693111150926</v>
       </c>
       <c r="X39" t="n">
-        <v>68.77298520347748</v>
+        <v>68.54731315765051</v>
       </c>
       <c r="Y39" t="n">
-        <v>68.68269577730436</v>
+        <v>68.45702373147739</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>42.8319801819373</v>
+        <v>42.60630813611033</v>
       </c>
       <c r="C40" t="n">
-        <v>30.24682109862783</v>
+        <v>30.02114905280087</v>
       </c>
       <c r="D40" t="n">
-        <v>11.61547301821236</v>
+        <v>11.38980097238539</v>
       </c>
       <c r="E40" t="n">
-        <v>9.433962646569171</v>
+        <v>9.208290600742203</v>
       </c>
       <c r="F40" t="n">
-        <v>8.421048022931245</v>
+        <v>8.195375977104277</v>
       </c>
       <c r="G40" t="n">
-        <v>30.99097935845876</v>
+        <v>30.76530731263179</v>
       </c>
       <c r="H40" t="n">
-        <v>25.22717250743958</v>
+        <v>25.00150046161261</v>
       </c>
       <c r="I40" t="n">
-        <v>18.45047492725828</v>
+        <v>18.22480288143132</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>40.29339137716948</v>
+        <v>40.06771933134252</v>
       </c>
       <c r="S40" t="n">
-        <v>87.01659803697225</v>
+        <v>86.79092599114529</v>
       </c>
       <c r="T40" t="n">
-        <v>90.94558942828149</v>
+        <v>90.71991738245453</v>
       </c>
       <c r="U40" t="n">
-        <v>149.3190293564909</v>
+        <v>149.0933573106639</v>
       </c>
       <c r="V40" t="n">
-        <v>115.137643323828</v>
+        <v>114.911971278001</v>
       </c>
       <c r="W40" t="n">
-        <v>149.522998336591</v>
+        <v>149.297326290764</v>
       </c>
       <c r="X40" t="n">
-        <v>88.70965538903715</v>
+        <v>88.48398334321018</v>
       </c>
       <c r="Y40" t="n">
-        <v>81.58465335209479</v>
+        <v>81.35898130626782</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>263.7338416634806</v>
+        <v>270.4983974269841</v>
       </c>
       <c r="C41" t="n">
-        <v>246.2728917710076</v>
+        <v>253.0374475345111</v>
       </c>
       <c r="D41" t="n">
-        <v>235.683041620683</v>
+        <v>242.4475973841865</v>
       </c>
       <c r="E41" t="n">
-        <v>262.9303700722618</v>
+        <v>269.6949258357653</v>
       </c>
       <c r="F41" t="n">
-        <v>287.8760457417114</v>
+        <v>294.640601505215</v>
       </c>
       <c r="G41" t="n">
-        <v>296.302737515135</v>
+        <v>303.0672932786386</v>
       </c>
       <c r="H41" t="n">
-        <v>220.4748021157671</v>
+        <v>227.2393578792707</v>
       </c>
       <c r="I41" t="n">
-        <v>91.47588957040591</v>
+        <v>98.24044533390945</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>30.86911794114968</v>
+        <v>37.63367370465322</v>
       </c>
       <c r="S41" t="n">
-        <v>90.02006958624534</v>
+        <v>96.78462534974888</v>
       </c>
       <c r="T41" t="n">
-        <v>104.0958495641314</v>
+        <v>110.8604053276349</v>
       </c>
       <c r="U41" t="n">
-        <v>132.3456529078365</v>
+        <v>139.11020867134</v>
       </c>
       <c r="V41" t="n">
-        <v>208.7522584701349</v>
+        <v>215.5168142336385</v>
       </c>
       <c r="W41" t="n">
-        <v>230.240968717413</v>
+        <v>237.0055244809166</v>
       </c>
       <c r="X41" t="n">
-        <v>250.731100678469</v>
+        <v>257.4956564419726</v>
       </c>
       <c r="Y41" t="n">
-        <v>267.2379386560536</v>
+        <v>274.0024944195571</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>47.53318364986734</v>
+        <v>54.29773941337088</v>
       </c>
       <c r="C42" t="n">
-        <v>53.70849898831574</v>
+        <v>60.47305475181928</v>
       </c>
       <c r="D42" t="n">
-        <v>28.44506556463875</v>
+        <v>35.20962132814229</v>
       </c>
       <c r="E42" t="n">
-        <v>38.64508045540094</v>
+        <v>45.40963621890448</v>
       </c>
       <c r="F42" t="n">
-        <v>26.06921239338388</v>
+        <v>32.83376815688742</v>
       </c>
       <c r="G42" t="n">
-        <v>18.34351716321063</v>
+        <v>25.10807292671417</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>52.68317110383782</v>
+        <v>59.44772686734136</v>
       </c>
       <c r="T42" t="n">
-        <v>81.1647286948216</v>
+        <v>87.92928445832514</v>
       </c>
       <c r="U42" t="n">
-        <v>106.9413820809748</v>
+        <v>113.7059378444784</v>
       </c>
       <c r="V42" t="n">
-        <v>113.8005871494253</v>
+        <v>120.5651429129288</v>
       </c>
       <c r="W42" t="n">
-        <v>132.6949831609196</v>
+        <v>139.4595389244232</v>
       </c>
       <c r="X42" t="n">
-        <v>86.77298520347748</v>
+        <v>93.53754096698101</v>
       </c>
       <c r="Y42" t="n">
-        <v>86.68269577730436</v>
+        <v>93.4472515408079</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>60.8319801819373</v>
+        <v>67.59653594544083</v>
       </c>
       <c r="C43" t="n">
-        <v>48.24682109862783</v>
+        <v>55.01137686213137</v>
       </c>
       <c r="D43" t="n">
-        <v>29.61547301821236</v>
+        <v>36.38002878171589</v>
       </c>
       <c r="E43" t="n">
-        <v>27.43396264656917</v>
+        <v>34.19851841007271</v>
       </c>
       <c r="F43" t="n">
-        <v>26.42104802293125</v>
+        <v>33.18560378643478</v>
       </c>
       <c r="G43" t="n">
-        <v>48.99097935845876</v>
+        <v>55.7555351219623</v>
       </c>
       <c r="H43" t="n">
-        <v>43.22717250743958</v>
+        <v>49.99172827094311</v>
       </c>
       <c r="I43" t="n">
-        <v>36.45047492725828</v>
+        <v>43.21503069076182</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>58.29339137716948</v>
+        <v>65.05794714067302</v>
       </c>
       <c r="S43" t="n">
-        <v>105.0165980369723</v>
+        <v>111.7811538004758</v>
       </c>
       <c r="T43" t="n">
-        <v>108.9455894282815</v>
+        <v>115.710145191785</v>
       </c>
       <c r="U43" t="n">
-        <v>167.3190293564909</v>
+        <v>174.0835851199944</v>
       </c>
       <c r="V43" t="n">
-        <v>133.137643323828</v>
+        <v>139.9021990873316</v>
       </c>
       <c r="W43" t="n">
-        <v>167.522998336591</v>
+        <v>174.2875541000946</v>
       </c>
       <c r="X43" t="n">
-        <v>106.7096553890372</v>
+        <v>113.4742111525407</v>
       </c>
       <c r="Y43" t="n">
-        <v>99.58465335209479</v>
+        <v>106.3492091155983</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>323511.2104088708</v>
+        <v>324718.0334293471</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>406581.2081455773</v>
+        <v>405846.2774541845</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>406581.2081455773</v>
+        <v>405846.2774541846</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>406581.2081455773</v>
+        <v>405846.2774541845</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>406581.2081455773</v>
+        <v>405846.2774541846</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>394443.0504088707</v>
+        <v>401175.7814945158</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>452435.1225254792</v>
+        <v>452668.5802568869</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>452435.1225254792</v>
+        <v>452668.580256887</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>452435.1225254792</v>
+        <v>452668.5802568869</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>452435.1225254792</v>
+        <v>452668.580256887</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>433814.1225254792</v>
+        <v>426816.1895881348</v>
       </c>
     </row>
     <row r="16">
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>901203.9725887424</v>
+      </c>
+      <c r="C2" t="n">
+        <v>901203.9725887423</v>
+      </c>
+      <c r="D2" t="n">
         <v>901203.9725887422</v>
       </c>
-      <c r="C2" t="n">
-        <v>901203.972588742</v>
-      </c>
-      <c r="D2" t="n">
-        <v>901203.972588742</v>
-      </c>
       <c r="E2" t="n">
-        <v>312559.1392073642</v>
+        <v>315057.6965629639</v>
       </c>
       <c r="F2" t="n">
-        <v>485198.9984604793</v>
+        <v>483582.2355276397</v>
       </c>
       <c r="G2" t="n">
-        <v>485198.9984604787</v>
+        <v>483582.2355276397</v>
       </c>
       <c r="H2" t="n">
-        <v>485198.9984604788</v>
+        <v>483582.2355276397</v>
       </c>
       <c r="I2" t="n">
-        <v>485198.9984604787</v>
+        <v>483582.2355276397</v>
       </c>
       <c r="J2" t="n">
-        <v>459413.5392073639</v>
+        <v>473480.276031482</v>
       </c>
       <c r="K2" t="n">
-        <v>590812.9409645482</v>
+        <v>591361.2518208536</v>
       </c>
       <c r="L2" t="n">
-        <v>590812.9409645483</v>
+        <v>591361.2518208536</v>
       </c>
       <c r="M2" t="n">
-        <v>590812.9409645483</v>
+        <v>591361.2518208536</v>
       </c>
       <c r="N2" t="n">
-        <v>590812.9409645484</v>
+        <v>591361.2518208534</v>
       </c>
       <c r="O2" t="n">
-        <v>547078.7009645482</v>
+        <v>530642.9951170799</v>
       </c>
       <c r="P2" t="n">
-        <v>236516.292169182</v>
+        <v>236516.2921691821</v>
       </c>
     </row>
     <row r="3">
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>22400</v>
+        <v>23162.22005967057</v>
       </c>
       <c r="F3" t="n">
-        <v>52800</v>
+        <v>51525.12403366765</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14400</v>
+        <v>19992.18224746441</v>
       </c>
       <c r="K3" t="n">
-        <v>95200</v>
+        <v>89788.35538919717</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26374,40 +26374,40 @@
         <v>467615.9599317312</v>
       </c>
       <c r="E4" t="n">
-        <v>183244.2248267481</v>
+        <v>184492.6945600646</v>
       </c>
       <c r="F4" t="n">
-        <v>269948.8600633092</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="G4" t="n">
-        <v>269948.8600633092</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="H4" t="n">
-        <v>269948.8600633092</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="I4" t="n">
-        <v>269948.8600633092</v>
+        <v>269137.2732849513</v>
       </c>
       <c r="J4" t="n">
-        <v>257039.5129975983</v>
+        <v>264092.5943250213</v>
       </c>
       <c r="K4" t="n">
-        <v>322237.8183648574</v>
+        <v>322503.3176792525</v>
       </c>
       <c r="L4" t="n">
-        <v>322237.8183648575</v>
+        <v>322503.3176792525</v>
       </c>
       <c r="M4" t="n">
-        <v>322237.8183648575</v>
+        <v>322503.3176792525</v>
       </c>
       <c r="N4" t="n">
-        <v>322237.8183648574</v>
+        <v>322503.3176792525</v>
       </c>
       <c r="O4" t="n">
-        <v>300640.8764081526</v>
+        <v>292518.7781685568</v>
       </c>
       <c r="P4" t="n">
-        <v>144745.8284464477</v>
+        <v>144738.4206832074</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>2353.932</v>
+        <v>2434.030847745557</v>
       </c>
       <c r="F5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="G5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="H5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="I5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="J5" t="n">
-        <v>7061.796</v>
+        <v>7515.485527185614</v>
       </c>
       <c r="K5" t="n">
-        <v>11517.453</v>
+        <v>11536.42502322063</v>
       </c>
       <c r="L5" t="n">
-        <v>11517.453</v>
+        <v>11536.42502322063</v>
       </c>
       <c r="M5" t="n">
-        <v>11517.453</v>
+        <v>11536.42502322063</v>
       </c>
       <c r="N5" t="n">
-        <v>11517.453</v>
+        <v>11536.42502322063</v>
       </c>
       <c r="O5" t="n">
-        <v>10004.211</v>
+        <v>9435.521561518022</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>399960.4126570112</v>
+      </c>
+      <c r="C6" t="n">
+        <v>399960.4126570111</v>
+      </c>
+      <c r="D6" t="n">
         <v>399960.412657011</v>
       </c>
-      <c r="C6" t="n">
-        <v>399960.4126570108</v>
-      </c>
-      <c r="D6" t="n">
-        <v>399960.4126570108</v>
-      </c>
       <c r="E6" t="n">
-        <v>104560.9823806162</v>
+        <v>104968.7510954832</v>
       </c>
       <c r="F6" t="n">
-        <v>154547.6523971701</v>
+        <v>155071.2252957922</v>
       </c>
       <c r="G6" t="n">
-        <v>207347.6523971695</v>
+        <v>206596.3493294598</v>
       </c>
       <c r="H6" t="n">
-        <v>207347.6523971696</v>
+        <v>206596.3493294598</v>
       </c>
       <c r="I6" t="n">
-        <v>207347.6523971695</v>
+        <v>206596.3493294598</v>
       </c>
       <c r="J6" t="n">
-        <v>180912.2302097655</v>
+        <v>181880.0139318107</v>
       </c>
       <c r="K6" t="n">
-        <v>161857.6695996907</v>
+        <v>167533.1537291832</v>
       </c>
       <c r="L6" t="n">
-        <v>257057.6695996908</v>
+        <v>257321.5091183804</v>
       </c>
       <c r="M6" t="n">
-        <v>257057.6695996908</v>
+        <v>257321.5091183804</v>
       </c>
       <c r="N6" t="n">
-        <v>257057.669599691</v>
+        <v>257321.5091183803</v>
       </c>
       <c r="O6" t="n">
-        <v>236433.6135563955</v>
+        <v>228688.6953870051</v>
       </c>
       <c r="P6" t="n">
-        <v>91770.4637227343</v>
+        <v>91777.87148597473</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J2" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K2" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="L2" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="M2" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="N2" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="O2" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26849,40 +26849,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>64.40640504208456</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>24.99022780933052</v>
       </c>
       <c r="K2" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,19 +26892,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26944,22 +26944,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -26968,25 +26968,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="K2" t="n">
-        <v>66</v>
+        <v>64.40640504208456</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>24.99022780933052</v>
       </c>
       <c r="P2" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
     </row>
     <row r="3">
@@ -28012,31 +28012,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="G11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="H11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="I11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="J11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -28057,31 +28057,31 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="R11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="S11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="T11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="U11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="V11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="W11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="X11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="Y11" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
     </row>
     <row r="12">
@@ -28091,37 +28091,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="G12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="H12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="I12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="J12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>20.60377358490566</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28133,34 +28133,34 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>28</v>
+        <v>21.30487222469803</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="R12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="S12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="T12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="U12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="V12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="W12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="X12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="Y12" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
     </row>
     <row r="13">
@@ -28170,76 +28170,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="G13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="H13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="I13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="J13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="K13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="L13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="M13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="N13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="O13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="P13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="R13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="S13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="T13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="U13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="V13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="W13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="X13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
       <c r="Y13" t="n">
-        <v>28</v>
+        <v>28.95277507458822</v>
       </c>
     </row>
     <row r="14">
@@ -28249,31 +28249,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -28294,31 +28294,31 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="15">
@@ -28328,37 +28328,37 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>68.69826461415894</v>
       </c>
       <c r="L15" t="n">
-        <v>69.53253955660031</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -28367,37 +28367,37 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="16">
@@ -28407,76 +28407,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="17">
@@ -28486,31 +28486,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -28531,31 +28531,31 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="18">
@@ -28565,31 +28565,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J18" t="n">
-        <v>94</v>
+        <v>68.69826461415839</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -28604,37 +28604,37 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P18" t="n">
-        <v>69.53253955660027</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="19">
@@ -28644,76 +28644,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J19" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="20">
@@ -28723,31 +28723,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -28768,31 +28768,31 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="21">
@@ -28802,40 +28802,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>94</v>
+        <v>68.69826461415894</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -28847,31 +28847,31 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>69.53253955660027</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="22">
@@ -28881,76 +28881,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J22" t="n">
-        <v>93.35918011667275</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="23">
@@ -28960,31 +28960,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J23" t="n">
-        <v>94</v>
+        <v>80.22321507513192</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -29005,31 +29005,31 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="24">
@@ -29039,37 +29039,37 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>69.53253955660027</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -29078,37 +29078,37 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P24" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="25">
@@ -29118,76 +29118,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J25" t="n">
-        <v>93.35918011667286</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="L25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="M25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="N25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="O25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="P25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Q25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="R25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="26">
@@ -29197,31 +29197,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -29242,31 +29242,31 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y26" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="27">
@@ -29276,37 +29276,37 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>61.81132075471698</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K27" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -29321,31 +29321,31 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>65.78242794726917</v>
       </c>
       <c r="R27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y27" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="28">
@@ -29355,76 +29355,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="L28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="M28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="N28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="O28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="P28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Q28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y28" t="n">
-        <v>84</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="29">
@@ -29434,31 +29434,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -29479,31 +29479,31 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y29" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="30">
@@ -29513,22 +29513,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -29537,52 +29537,52 @@
         <v>99.52238</v>
       </c>
       <c r="J30" t="n">
-        <v>8.834986034614321</v>
+        <v>126.8376266666667</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>137.225672045827</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>137</v>
+        <v>14.98112516938904</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y30" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J31" t="n">
         <v>126.9954214393961</v>
@@ -29628,40 +29628,40 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>137.225672045827</v>
       </c>
       <c r="P31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Q31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y31" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="32">
@@ -29671,31 +29671,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -29716,31 +29716,31 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y32" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="33">
@@ -29750,22 +29750,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
@@ -29774,52 +29774,52 @@
         <v>99.52238</v>
       </c>
       <c r="J33" t="n">
-        <v>75.45153460770248</v>
+        <v>126.8376266666667</v>
       </c>
       <c r="K33" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>137.225672045827</v>
       </c>
       <c r="M33" t="n">
-        <v>137</v>
+        <v>129.7238717677569</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R33" t="n">
-        <v>137</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y33" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J34" t="n">
         <v>126.9954214393961</v>
@@ -29871,34 +29871,34 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Q34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y34" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="35">
@@ -29908,31 +29908,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -29953,31 +29953,31 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y35" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="36">
@@ -29987,22 +29987,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H36" t="n">
         <v>112.2354442364965</v>
@@ -30011,22 +30011,22 @@
         <v>99.52238</v>
       </c>
       <c r="J36" t="n">
-        <v>126.8376266666667</v>
+        <v>76.38402853292025</v>
       </c>
       <c r="K36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="L36" t="n">
-        <v>91.27219585770244</v>
+        <v>137.225672045827</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>137.225672045827</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="P36" t="n">
         <v>133.9744074143302</v>
@@ -30035,28 +30035,28 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y36" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J37" t="n">
         <v>126.9954214393961</v>
@@ -30108,34 +30108,34 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Q37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y37" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="38">
@@ -30145,31 +30145,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -30190,31 +30190,31 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y38" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="39">
@@ -30224,22 +30224,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -30251,49 +30251,49 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="L39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>137.225672045827</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R39" t="n">
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y39" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="40">
@@ -30303,31 +30303,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="C40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="D40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="E40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="F40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="G40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="H40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="I40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="J40" t="n">
-        <v>126.9954214393961</v>
+        <v>97.60334416542197</v>
       </c>
       <c r="K40" t="n">
         <v>129.0132581705354</v>
@@ -30345,34 +30345,34 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>115.9568254442556</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Q40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="R40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="S40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="T40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="U40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="V40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="W40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="X40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
       <c r="Y40" t="n">
-        <v>137</v>
+        <v>137.225672045827</v>
       </c>
     </row>
     <row r="41">
@@ -30382,31 +30382,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="C41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="D41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="E41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="F41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="G41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="H41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="J41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -30427,31 +30427,31 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>79.62784025503144</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="R41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="S41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="T41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="U41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="V41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="W41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="X41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Y41" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
     </row>
     <row r="42">
@@ -30461,22 +30461,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="C42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="D42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="E42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="F42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="G42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -30485,52 +30485,52 @@
         <v>99.52238</v>
       </c>
       <c r="J42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="K42" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="M42" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>119</v>
+        <v>24.79067432035109</v>
       </c>
       <c r="O42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="P42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="R42" t="n">
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="T42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="U42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="V42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="W42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="X42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Y42" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
     </row>
     <row r="43">
@@ -30540,34 +30540,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="C43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="D43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="E43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="F43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="G43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="H43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="J43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="K43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -30582,34 +30582,34 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Q43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="R43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="S43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="T43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="U43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="V43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="W43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="X43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="Y43" t="n">
-        <v>119</v>
+        <v>112.2354442364965</v>
       </c>
     </row>
     <row r="44">
